--- a/data/reports/2024-10-07/2024-10-07_duplicates.xlsx
+++ b/data/reports/2024-10-07/2024-10-07_duplicates.xlsx
@@ -185,7 +185,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=34a57d161b667c10dabd2f41f54bcb14&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004139</t>
+    <t>RMD0009352</t>
   </si>
   <si>
     <t>Global Net Holdings, Inc.</t>
@@ -201,28 +201,28 @@
     <t>CEO</t>
   </si>
   <si>
+    <t>Financial</t>
+  </si>
+  <si>
+    <t>800-7096314</t>
+  </si>
+  <si>
+    <t>2024-03-29</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b379943f1be37810cc2f2f82f54bcbf5&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004139</t>
+  </si>
+  <si>
     <t>Sales</t>
   </si>
   <si>
     <t>800-709-6314</t>
   </si>
   <si>
-    <t>2024-03-29</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c77b62251b09741002beea82f54bcb87&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009352</t>
-  </si>
-  <si>
-    <t>Financial</t>
-  </si>
-  <si>
-    <t>800-7096314</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b379943f1be37810cc2f2f82f54bcbf5&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008972</t>
@@ -261,7 +261,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=bfc7bfc81b9f74505eb762cfe54bcbe5&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009020</t>
+    <t>RMD0009019</t>
   </si>
   <si>
     <t>Enhanced Telecommunications &amp; Data, Inc.</t>
@@ -277,6 +277,24 @@
     <t>Engineer</t>
   </si>
   <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>208-947-3900</t>
+  </si>
+  <si>
+    <t>3904</t>
+  </si>
+  <si>
+    <t>2024-04-09</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5e6e01191b57f010222b0e9ee54bcb7a&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0009020</t>
+  </si>
+  <si>
     <t>IT Department</t>
   </si>
   <si>
@@ -286,25 +304,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=bcd785dd1b17f010222b0e9ee54bcb74&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009019</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>208-947-3900</t>
-  </si>
-  <si>
-    <t>3904</t>
-  </si>
-  <si>
-    <t>2024-04-09</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5e6e01191b57f010222b0e9ee54bcb7a&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009084</t>
+    <t>RMD0009205</t>
   </si>
   <si>
     <t>ADCOM Technologies, LLC</t>
@@ -318,12 +318,6 @@
     <t>ON DEMAND Communications</t>
   </si>
   <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=fd73904e1b1bf010031f0f21f54bcb87&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009205</t>
-  </si>
-  <si>
     <t>Dean Franks</t>
   </si>
   <si>
@@ -346,7 +340,13 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=53ad1e731b53b0109294113d9c4bcb6a&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008869</t>
+    <t>RMD0009084</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=fd73904e1b1bf010031f0f21f54bcb87&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0006774</t>
   </si>
   <si>
     <t>Sage Communications, Inc.</t>
@@ -356,9 +356,18 @@
 Camarillo CA 93012</t>
   </si>
   <si>
+    <t>NONE</t>
+  </si>
+  <si>
     <t>Sage Network &amp; Communications</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612a08851bbef010e1ca848ce54bcbb3&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008869</t>
+  </si>
+  <si>
     <t>Rick Minyard</t>
   </si>
   <si>
@@ -378,15 +387,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ed3d8a531b0334509ac2ea04bc4bcb27&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0006774</t>
-  </si>
-  <si>
-    <t>NONE</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612a08851bbef010e1ca848ce54bcbb3&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0004389</t>
@@ -409,7 +409,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=fab855e51b09741064c4426de54bcbf6&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004724</t>
+    <t>RMD0005819</t>
   </si>
   <si>
     <t>Ton80 Communications, LLC</t>
@@ -419,16 +419,16 @@
 Anderson SC 29642</t>
   </si>
   <si>
+    <t>4109121000</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=aab7f5961b667c10dabd2f41f54bcb9f&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004724</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=6239f4c21bcdf41002beea82f54bcb2a&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005819</t>
-  </si>
-  <si>
-    <t>4109121000</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=aab7f5961b667c10dabd2f41f54bcb9f&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0004849</t>
@@ -493,10 +493,37 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=eb20864e1bea3c105e240f6fe54bcbf1&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0003758</t>
+  </si>
+  <si>
+    <t>Matchcom Telecommunications Inc.</t>
+  </si>
+  <si>
+    <t>1680 Michigan Ave
+Ste 700
+Miami Beach Florida 33139</t>
+  </si>
+  <si>
+    <t>Davon Person</t>
+  </si>
+  <si>
+    <t>Director of Operations</t>
+  </si>
+  <si>
+    <t>Network Operations Center</t>
+  </si>
+  <si>
+    <t>1250 E Hallandale Beach Blvd
+Hallandale FL 33009</t>
+  </si>
+  <si>
+    <t>9546248162</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=494bb99d1bcdf0109294113d9c4bcb26&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0007488</t>
-  </si>
-  <si>
-    <t>Matchcom Telecommunications Inc.</t>
   </si>
   <si>
     <t>1680 Michigan Ave
@@ -528,33 +555,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=267cc9661b3ef410aa3cea41f54bcbcd&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0003758</t>
-  </si>
-  <si>
-    <t>1680 Michigan Ave
-Ste 700
-Miami Beach Florida 33139</t>
-  </si>
-  <si>
-    <t>Davon Person</t>
-  </si>
-  <si>
-    <t>Director of Operations</t>
-  </si>
-  <si>
-    <t>Network Operations Center</t>
-  </si>
-  <si>
-    <t>1250 E Hallandale Beach Blvd
-Hallandale FL 33009</t>
-  </si>
-  <si>
-    <t>9546248162</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=494bb99d1bcdf0109294113d9c4bcb26&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0005139</t>
@@ -711,7 +711,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=76af51511bc9f0102eb2a82fe54bcb18&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008577</t>
+    <t>RMD0005040</t>
   </si>
   <si>
     <t>Dialect, LLC</t>
@@ -721,6 +721,12 @@
 Phoenix AZ 85008</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=f58908e11b793c10680f657ae54bcb6d&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008577</t>
+  </si>
+  <si>
     <t>BatchDialer</t>
   </si>
   <si>
@@ -739,13 +745,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ee4909b01b8f7c10aa3cea41f54bcb77&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005040</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=f58908e11b793c10680f657ae54bcb6d&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005569</t>
+    <t>RMD0005461</t>
   </si>
   <si>
     <t>Valstarr Asia</t>
@@ -755,25 +755,10 @@
 Valley Center CA 92082</t>
   </si>
   <si>
+    <t>0031217672</t>
+  </si>
+  <si>
     <t>Vincent W. Kahn</t>
-  </si>
-  <si>
-    <t>Owner</t>
-  </si>
-  <si>
-    <t>Systems Admin</t>
-  </si>
-  <si>
-    <t>'+13213288217</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=93ebdbd01b227810ca5aec21f54bcbd6&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005461</t>
-  </si>
-  <si>
-    <t>0031217672</t>
   </si>
   <si>
     <t>MANAGER</t>
@@ -793,7 +778,22 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612913461bd6f010ca5aec21f54bcbac&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005297</t>
+    <t>RMD0005569</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>Systems Admin</t>
+  </si>
+  <si>
+    <t>'+13213288217</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=93ebdbd01b227810ca5aec21f54bcbd6&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007936</t>
   </si>
   <si>
     <t>STREAMLINE SELLERS PTY LTD</t>
@@ -806,25 +806,25 @@
     <t>Australia</t>
   </si>
   <si>
+    <t>Syed Omar Farooq Shah</t>
+  </si>
+  <si>
+    <t>Director</t>
+  </si>
+  <si>
+    <t>'+61406851546</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=6273a2321b3638109ac2ea04bc4bcb55&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0005297</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d24a9a271bca3810d49ca86ce54bcb20&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007936</t>
-  </si>
-  <si>
-    <t>Syed Omar Farooq Shah</t>
-  </si>
-  <si>
-    <t>Director</t>
-  </si>
-  <si>
-    <t>'+61406851546</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=6273a2321b3638109ac2ea04bc4bcb55&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005574</t>
+    <t>RMD0005585</t>
   </si>
   <si>
     <t>MegaClec, Inc</t>
@@ -838,6 +838,28 @@
     <t>0012465480</t>
   </si>
   <si>
+    <t>Voiceay, Voiceway Netoworks, Meganet,  Troy City Internet Exchange</t>
+  </si>
+  <si>
+    <t>Paul Joncas</t>
+  </si>
+  <si>
+    <t>Operatopms</t>
+  </si>
+  <si>
+    <t>187 Plymouth Avenue
+Fall River MA 02721</t>
+  </si>
+  <si>
+    <t>5086460030</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c9f5735c1ba2781002beea82f54bcbaf&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0005574</t>
+  </si>
+  <si>
     <t>Troy City Internet Exchange;Voiceway;Meganet Communications</t>
   </si>
   <si>
@@ -845,29 +867,20 @@
 Fall River MA 02721</t>
   </si>
   <si>
-    <t>5086460030</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1426e7581ba678109294113d9c4bcb2f&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005585</t>
-  </si>
-  <si>
-    <t>Voiceay, Voiceway Netoworks, Meganet,  Troy City Internet Exchange</t>
-  </si>
-  <si>
-    <t>Paul Joncas</t>
-  </si>
-  <si>
-    <t>Operatopms</t>
-  </si>
-  <si>
-    <t>187 Plymouth Avenue
-Fall River MA 02721</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c9f5735c1ba2781002beea82f54bcbaf&amp;view=sp</t>
+    <t>RMD0006284</t>
+  </si>
+  <si>
+    <t>Office No 17 3rd Floor Anique Arcade Plaza I8 Markaz
+  Islamabad, Pakistan</t>
+  </si>
+  <si>
+    <t>Pakistan</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=3acc71c31b2a305064c4426de54bcb40&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0007962</t>
@@ -877,9 +890,6 @@
 federal 46000 Islamabad, Pakistan</t>
   </si>
   <si>
-    <t>Pakistan</t>
-  </si>
-  <si>
     <t>Umair Hassan</t>
   </si>
   <si>
@@ -890,16 +900,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8037e23e1b32781093d3a820f54bcb1c&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0006284</t>
-  </si>
-  <si>
-    <t>Office No 17 3rd Floor Anique Arcade Plaza I8 Markaz
-  Islamabad, Pakistan</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=3acc71c31b2a305064c4426de54bcb40&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008125</t>
@@ -931,7 +931,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=3cc1fbbe1b7a3810dcd1ed3be54bcbe8&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007626</t>
+    <t>RMD0007575</t>
   </si>
   <si>
     <t>Turcios Parada SA</t>
@@ -944,16 +944,16 @@
     <t>El Salvador</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=cfeb296a1bf6f410680f657ae54bcbeb&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007626</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5b6a75a61b3af410680f657ae54bcbbd&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007575</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=cfeb296a1bf6f410680f657ae54bcbeb&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007716</t>
+    <t>RMD0007696</t>
   </si>
   <si>
     <t>High Country Internet</t>
@@ -963,16 +963,16 @@
 Tucson AZ 85719</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=e3d356aa1b3ef410165aedfde54bcb51&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007716</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=4a516ea21b7ef410165aedfde54bcbd3&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007696</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=e3d356aa1b3ef410165aedfde54bcb51&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007944</t>
+    <t>RMD0007939</t>
   </si>
   <si>
     <t>Conquest Solutions</t>
@@ -982,6 +982,12 @@
 Marietta GA 30067</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d225a2fe1b7a3810e4ccdb1de54bcbff&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007944</t>
+  </si>
+  <si>
     <t>Lance Retter</t>
   </si>
   <si>
@@ -997,13 +1003,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c186e6321bba3810e4ccdb1de54bcb5a&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007939</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d225a2fe1b7a3810e4ccdb1de54bcbff&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008423</t>
+    <t>RMD0008393</t>
   </si>
   <si>
     <t>Your Business I.T. Inc.</t>
@@ -1011,6 +1011,12 @@
   <si>
     <t>295 Weber St. N
 Ontario N2J 3H8 Waterloo, Canada</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=545854ef1b7ab810d39dddb6bc4bcb74&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008423</t>
   </si>
   <si>
     <t>Your Business I.T.</t>
@@ -1028,13 +1034,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=761bc9e71b3eb810d39dddb6bc4bcbe0&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008393</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=545854ef1b7ab810d39dddb6bc4bcb74&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008451</t>
+    <t>RMD0008450</t>
   </si>
   <si>
     <t>WTS</t>
@@ -1044,12 +1044,6 @@
 Greensboro NC 27401</t>
   </si>
   <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d7e7ad2b1bbeb81093d3a820f54bcb5c&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008450</t>
-  </si>
-  <si>
     <t>null
 null NC</t>
   </si>
@@ -1057,7 +1051,13 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b746a9e71bbeb81093d3a820f54bcb4c&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008610</t>
+    <t>RMD0008451</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d7e7ad2b1bbeb81093d3a820f54bcb5c&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008612</t>
   </si>
   <si>
     <t>Liberty Wealth Planners</t>
@@ -1067,43 +1067,49 @@
  110065 Dehli, India</t>
   </si>
   <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Bharat Raj</t>
+  </si>
+  <si>
+    <t>'+919836963636</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=21f229c51b0bbc1093d3a820f54bcbdb&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008611</t>
+  </si>
+  <si>
     <t>Bangladesh</t>
   </si>
   <si>
+    <t>Nobe</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8ce1e5851b0bbc1093d3a820f54bcba5&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008610</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9c9129851b0bbc1093d3a820f54bcb97&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008612</t>
-  </si>
-  <si>
-    <t>India</t>
-  </si>
-  <si>
-    <t>Bharat Raj</t>
-  </si>
-  <si>
-    <t>'+919836963636</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=21f229c51b0bbc1093d3a820f54bcbdb&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008611</t>
-  </si>
-  <si>
-    <t>Nobe</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8ce1e5851b0bbc1093d3a820f54bcba5&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008759</t>
+    <t>RMD0008756</t>
   </si>
   <si>
     <t>573 Ocean Blvd
 Hampton NH 03842</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9bf181421b0b3050003c43f1f54bcbe8&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008759</t>
+  </si>
+  <si>
     <t>Jeffrey D Houston</t>
   </si>
   <si>
@@ -1116,13 +1122,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=46724d021b0b3050003c43f1f54bcb05&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008756</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9bf181421b0b3050003c43f1f54bcbe8&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008755</t>
+    <t>RMD0008798</t>
   </si>
   <si>
     <t>Aspire Holdings Group LLC</t>
@@ -1135,30 +1135,30 @@
     <t>AspirePBX</t>
   </si>
   <si>
+    <t>CP Short</t>
+  </si>
+  <si>
+    <t>Member</t>
+  </si>
+  <si>
+    <t>Partner</t>
+  </si>
+  <si>
+    <t>6023888700</t>
+  </si>
+  <si>
+    <t>725</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9cda6ace1b8f30505eb762cfe54bcb49&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008755</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=82b1054a1b0f30508d57ecace54bcbda&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008798</t>
-  </si>
-  <si>
-    <t>CP Short</t>
-  </si>
-  <si>
-    <t>Member</t>
-  </si>
-  <si>
-    <t>Partner</t>
-  </si>
-  <si>
-    <t>6023888700</t>
-  </si>
-  <si>
-    <t>725</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9cda6ace1b8f30505eb762cfe54bcb49&amp;view=sp</t>
-  </si>
-  <si>
     <t>RMD0008787</t>
   </si>
   <si>
@@ -1186,7 +1186,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=29f1aec61b0f3050003c43f1f54bcba5&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009161</t>
+    <t>RMD0009160</t>
   </si>
   <si>
     <t>MCE Systems</t>
@@ -1196,16 +1196,16 @@
 Irvine CA 92604</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8975f3e61b577410503110ad9c4bcbcf&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0009161</t>
+  </si>
+  <si>
     <t>9497014500</t>
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=2338b76a1b577410503110ad9c4bcb43&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009160</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8975f3e61b577410503110ad9c4bcbcf&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0009453</t>
@@ -6312,9 +6312,15 @@
       <c r="F7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
+      <c r="G7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J7" s="1" t="s">
         <v>58</v>
       </c>
@@ -6372,15 +6378,9 @@
       <c r="F8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
       <c r="J8" s="1" t="s">
         <v>58</v>
       </c>
@@ -6555,9 +6555,11 @@
       <c r="O11" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="P11" s="1"/>
+      <c r="P11" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="Q11" s="1" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="R11" s="1" t="s">
         <v>34</v>
@@ -6568,14 +6570,16 @@
       <c r="T11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U11" s="1"/>
+      <c r="U11" s="1" t="s">
+        <v>86</v>
+      </c>
       <c r="V11" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B12" s="1">
         <v>21520390</v>
@@ -6602,7 +6606,7 @@
         <v>82</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>80</v>
@@ -6611,13 +6615,11 @@
         <v>27</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="P12" s="1" t="s">
-        <v>89</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="P12" s="1"/>
       <c r="Q12" s="1" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="R12" s="1" t="s">
         <v>34</v>
@@ -6628,9 +6630,7 @@
       <c r="T12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U12" s="1" t="s">
-        <v>90</v>
-      </c>
+      <c r="U12" s="1"/>
       <c r="V12" s="1" t="s">
         <v>91</v>
       </c>
@@ -6649,41 +6649,55 @@
         <v>94</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
         <v>95</v>
       </c>
       <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
+      <c r="J13" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="P13" s="1"/>
-      <c r="Q13" s="1"/>
+      <c r="Q13" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="R13" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S13" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U13" s="1"/>
       <c r="V13" s="1" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B14" s="1">
         <v>23003460</v>
@@ -6695,46 +6709,32 @@
         <v>94</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
         <v>95</v>
       </c>
       <c r="I14" s="1"/>
-      <c r="J14" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O14" s="1" t="s">
-        <v>102</v>
-      </c>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
       <c r="P14" s="1"/>
-      <c r="Q14" s="1" t="s">
-        <v>103</v>
-      </c>
+      <c r="Q14" s="1"/>
       <c r="R14" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S14" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U14" s="1"/>
       <c r="V14" s="1" t="s">
@@ -6760,54 +6760,40 @@
       <c r="F15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G15" s="1"/>
+      <c r="G15" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="H15" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I15" s="1"/>
-      <c r="J15" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="K15" s="1" t="s">
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="P15" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="S15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="V15" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B16" s="1">
         <v>23250467</v>
@@ -6824,33 +6810,47 @@
       <c r="F16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="1"/>
+      <c r="H16" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U16" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T16" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="U16" s="1"/>
       <c r="V16" s="1" t="s">
         <v>118</v>
       </c>
@@ -6969,16 +6969,28 @@
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
+      <c r="J19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="M19" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
+        <v>127</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="P19" s="1"/>
-      <c r="Q19" s="1"/>
+      <c r="Q19" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="R19" s="1" t="s">
         <v>26</v>
       </c>
@@ -6986,16 +6998,16 @@
         <v>26</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U19" s="1"/>
       <c r="V19" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B20" s="1">
         <v>25462672</v>
@@ -7015,28 +7027,16 @@
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
-      <c r="J20" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
       <c r="M20" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O20" s="1" t="s">
-        <v>130</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
       <c r="P20" s="1"/>
-      <c r="Q20" s="1" t="s">
-        <v>53</v>
-      </c>
+      <c r="Q20" s="1"/>
       <c r="R20" s="1" t="s">
         <v>26</v>
       </c>
@@ -7044,7 +7044,7 @@
         <v>26</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U20" s="1"/>
       <c r="V20" s="1" t="s">
@@ -7289,31 +7289,27 @@
       <c r="O25" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="P25" s="1" t="s">
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="U25" s="1"/>
+      <c r="V25" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="Q25" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U25" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="V25" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="A26" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B26" s="1">
         <v>27710730</v>
@@ -7322,7 +7318,7 @@
         <v>152</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>26</v>
@@ -7334,37 +7330,41 @@
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="L26" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="M26" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="L26" s="1" t="s">
+      <c r="N26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O26" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="M26" s="1" t="s">
+      <c r="P26" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="N26" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O26" s="1" t="s">
+      <c r="Q26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="R26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U26" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="P26" s="1"/>
-      <c r="Q26" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T26" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="U26" s="1"/>
       <c r="V26" s="1" t="s">
         <v>169</v>
       </c>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="P30" s="1"/>
       <c r="Q30" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R30" s="1" t="s">
         <v>34</v>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="P31" s="1"/>
       <c r="Q31" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R31" s="1" t="s">
         <v>34</v>
@@ -7828,48 +7828,34 @@
       </c>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
-      <c r="I35" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>222</v>
-      </c>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
       <c r="M35" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="N35" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O35" s="1" t="s">
-        <v>223</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
       <c r="P35" s="1"/>
-      <c r="Q35" s="1" t="s">
-        <v>53</v>
-      </c>
+      <c r="Q35" s="1"/>
       <c r="R35" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S35" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T35" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U35" s="1"/>
       <c r="V35" s="1" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="36" spans="1:22">
       <c r="A36" s="1" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B36" s="1">
         <v>31124688</v>
@@ -7888,25 +7874,39 @@
       </c>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
+      <c r="I36" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>224</v>
+      </c>
       <c r="M36" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N36" s="1"/>
-      <c r="O36" s="1"/>
+        <v>218</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>225</v>
+      </c>
       <c r="P36" s="1"/>
-      <c r="Q36" s="1"/>
+      <c r="Q36" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="R36" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S36" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T36" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U36" s="1"/>
       <c r="V36" s="1" t="s">
@@ -7932,48 +7932,54 @@
       <c r="F37" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
+      <c r="G37" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J37" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="N37" s="1" t="s">
         <v>27</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P37" s="1"/>
       <c r="Q37" s="1" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S37" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U37" s="1"/>
       <c r="V37" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="38" spans="1:22">
       <c r="A38" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B38" s="1">
         <v>31217029</v>
@@ -7990,26 +7996,20 @@
       <c r="F38" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G38" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
       <c r="J38" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="N38" s="1" t="s">
         <v>27</v>
@@ -8019,16 +8019,16 @@
       </c>
       <c r="P38" s="1"/>
       <c r="Q38" s="1" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="R38" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S38" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U38" s="1"/>
       <c r="V38" s="1" t="s">
@@ -8057,33 +8057,45 @@
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
+      <c r="J39" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>189</v>
+      </c>
       <c r="M39" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N39" s="1"/>
-      <c r="O39" s="1"/>
+        <v>244</v>
+      </c>
+      <c r="N39" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>248</v>
+      </c>
       <c r="P39" s="1"/>
-      <c r="Q39" s="1"/>
+      <c r="Q39" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="R39" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S39" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U39" s="1"/>
       <c r="V39" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="40" spans="1:22">
       <c r="A40" s="1" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B40" s="1">
         <v>31294614</v>
@@ -8103,36 +8115,24 @@
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
-      <c r="J40" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="L40" s="1" t="s">
-        <v>189</v>
-      </c>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
       <c r="M40" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="N40" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="O40" s="1" t="s">
-        <v>250</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N40" s="1"/>
+      <c r="O40" s="1"/>
       <c r="P40" s="1"/>
-      <c r="Q40" s="1" t="s">
-        <v>103</v>
-      </c>
+      <c r="Q40" s="1"/>
       <c r="R40" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S40" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U40" s="1"/>
       <c r="V40" s="1" t="s">
@@ -8164,42 +8164,48 @@
       <c r="H41" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="I41" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>258</v>
+      </c>
       <c r="M41" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N41" s="1" t="s">
         <v>27</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="P41" s="1"/>
       <c r="Q41" s="1" t="s">
-        <v>103</v>
+        <v>33</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S41" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="U41" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="U41" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="V41" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="42" spans="1:22">
       <c r="A42" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B42" s="1">
         <v>31356652</v>
@@ -8220,18 +8226,14 @@
         <v>255</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="L42" s="1" t="s">
         <v>263</v>
       </c>
+      <c r="I42" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
       <c r="M42" s="1" t="s">
         <v>264</v>
       </c>
@@ -8239,24 +8241,22 @@
         <v>27</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="P42" s="1"/>
       <c r="Q42" s="1" t="s">
-        <v>33</v>
+        <v>101</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S42" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U42" s="1" t="s">
-        <v>62</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="U42" s="1"/>
       <c r="V42" s="1" t="s">
         <v>265</v>
       </c>
@@ -8278,55 +8278,49 @@
       <c r="F43" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="L43" s="1" t="s">
-        <v>270</v>
-      </c>
+      <c r="G43" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
       <c r="M43" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="N43" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="O43" s="1" t="s">
-        <v>271</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N43" s="1"/>
+      <c r="O43" s="1"/>
       <c r="P43" s="1"/>
-      <c r="Q43" s="1" t="s">
-        <v>103</v>
-      </c>
+      <c r="Q43" s="1"/>
       <c r="R43" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S43" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U43" s="1"/>
       <c r="V43" s="1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="44" spans="1:22">
       <c r="A44" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B44" s="1">
         <v>31392434</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>34</v>
@@ -8334,33 +8328,39 @@
       <c r="F44" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="G44" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>273</v>
+      </c>
       <c r="M44" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N44" s="1"/>
-      <c r="O44" s="1"/>
+        <v>271</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="O44" s="1" t="s">
+        <v>274</v>
+      </c>
       <c r="P44" s="1"/>
-      <c r="Q44" s="1"/>
+      <c r="Q44" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="R44" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S44" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U44" s="1"/>
       <c r="V44" s="1" t="s">
@@ -8408,7 +8408,7 @@
         <v>281</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="Q45" s="1" t="s">
         <v>33</v>
@@ -8498,9 +8498,7 @@
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
-      <c r="M47" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="M47" s="1"/>
       <c r="N47" s="1"/>
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
@@ -8544,7 +8542,9 @@
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
-      <c r="M48" s="1"/>
+      <c r="M48" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
       <c r="P48" s="1"/>
@@ -8582,15 +8582,9 @@
       <c r="F49" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G49" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I49" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
@@ -8634,9 +8628,15 @@
       <c r="F50" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
+      <c r="G50" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
@@ -8675,55 +8675,41 @@
         <v>300</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
-      <c r="J51" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="K51" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="L51" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
       <c r="M51" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="N51" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O51" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="P51" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="Q51" s="1" t="s">
-        <v>33</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N51" s="1"/>
+      <c r="O51" s="1"/>
+      <c r="P51" s="1"/>
+      <c r="Q51" s="1"/>
       <c r="R51" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S51" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T51" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U51" s="1"/>
       <c r="V51" s="1" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="52" spans="1:22">
       <c r="A52" s="1" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B52" s="1">
         <v>31445216</v>
@@ -8735,32 +8721,46 @@
         <v>300</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
-      <c r="J52" s="1"/>
-      <c r="K52" s="1"/>
-      <c r="L52" s="1"/>
+      <c r="J52" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>83</v>
+      </c>
       <c r="M52" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N52" s="1"/>
-      <c r="O52" s="1"/>
-      <c r="P52" s="1"/>
-      <c r="Q52" s="1"/>
+        <v>300</v>
+      </c>
+      <c r="N52" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O52" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="P52" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="Q52" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="R52" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S52" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T52" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U52" s="1"/>
       <c r="V52" s="1" t="s">
@@ -8789,43 +8789,33 @@
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
-      <c r="J53" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>280</v>
-      </c>
+      <c r="J53" s="1"/>
+      <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="N53" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="O53" s="1" t="s">
-        <v>313</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N53" s="1"/>
+      <c r="O53" s="1"/>
       <c r="P53" s="1"/>
-      <c r="Q53" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="Q53" s="1"/>
       <c r="R53" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S53" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U53" s="1"/>
       <c r="V53" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="54" spans="1:22">
       <c r="A54" s="1" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B54" s="1">
         <v>31455868</v>
@@ -8845,24 +8835,34 @@
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
+      <c r="J54" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>280</v>
+      </c>
       <c r="L54" s="1"/>
       <c r="M54" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N54" s="1"/>
-      <c r="O54" s="1"/>
+        <v>314</v>
+      </c>
+      <c r="N54" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>315</v>
+      </c>
       <c r="P54" s="1"/>
-      <c r="Q54" s="1"/>
+      <c r="Q54" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="R54" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S54" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U54" s="1"/>
       <c r="V54" s="1" t="s">
@@ -8895,7 +8895,7 @@
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
       <c r="M55" s="1" t="s">
-        <v>40</v>
+        <v>320</v>
       </c>
       <c r="N55" s="1"/>
       <c r="O55" s="1"/>
@@ -8912,12 +8912,12 @@
       </c>
       <c r="U55" s="1"/>
       <c r="V55" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:22">
       <c r="A56" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B56" s="1">
         <v>31457815</v>
@@ -8941,7 +8941,7 @@
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
       <c r="M56" s="1" t="s">
-        <v>322</v>
+        <v>40</v>
       </c>
       <c r="N56" s="1"/>
       <c r="O56" s="1"/>
@@ -8983,33 +8983,45 @@
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
-      <c r="J57" s="1"/>
-      <c r="K57" s="1"/>
-      <c r="L57" s="1"/>
+      <c r="J57" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="M57" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N57" s="1"/>
-      <c r="O57" s="1"/>
+        <v>326</v>
+      </c>
+      <c r="N57" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="O57" s="1" t="s">
+        <v>329</v>
+      </c>
       <c r="P57" s="1"/>
-      <c r="Q57" s="1"/>
+      <c r="Q57" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="R57" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S57" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U57" s="1"/>
       <c r="V57" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="58" spans="1:22">
       <c r="A58" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B58" s="1">
         <v>31475270</v>
@@ -9024,50 +9036,40 @@
         <v>34</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="L58" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="I58" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="J58" s="1"/>
+      <c r="K58" s="1"/>
+      <c r="L58" s="1"/>
       <c r="M58" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="N58" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="O58" s="1" t="s">
-        <v>332</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N58" s="1"/>
+      <c r="O58" s="1"/>
       <c r="P58" s="1"/>
-      <c r="Q58" s="1" t="s">
-        <v>103</v>
-      </c>
+      <c r="Q58" s="1"/>
       <c r="R58" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S58" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U58" s="1"/>
       <c r="V58" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="59" spans="1:22">
       <c r="A59" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B59" s="1">
         <v>31475270</v>
@@ -9082,13 +9084,11 @@
         <v>34</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
-      <c r="I59" s="1" t="s">
-        <v>335</v>
-      </c>
+      <c r="I59" s="1"/>
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
@@ -9125,53 +9125,41 @@
         <v>338</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
-      <c r="J60" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="K60" s="1" t="s">
-        <v>280</v>
-      </c>
+      <c r="J60" s="1"/>
+      <c r="K60" s="1"/>
       <c r="L60" s="1"/>
       <c r="M60" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="N60" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O60" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="P60" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="Q60" s="1" t="s">
-        <v>53</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N60" s="1"/>
+      <c r="O60" s="1"/>
+      <c r="P60" s="1"/>
+      <c r="Q60" s="1"/>
       <c r="R60" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S60" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U60" s="1"/>
       <c r="V60" s="1" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="61" spans="1:22">
       <c r="A61" s="1" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B61" s="1">
         <v>31485048</v>
@@ -9181,32 +9169,44 @@
         <v>338</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
-      <c r="J61" s="1"/>
-      <c r="K61" s="1"/>
+      <c r="J61" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>280</v>
+      </c>
       <c r="L61" s="1"/>
       <c r="M61" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N61" s="1"/>
-      <c r="O61" s="1"/>
-      <c r="P61" s="1"/>
-      <c r="Q61" s="1"/>
+        <v>338</v>
+      </c>
+      <c r="N61" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O61" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="P61" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="Q61" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="R61" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S61" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U61" s="1"/>
       <c r="V61" s="1" t="s">
@@ -9227,43 +9227,57 @@
         <v>347</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G62" s="1"/>
       <c r="H62" s="1" t="s">
         <v>348</v>
       </c>
       <c r="I62" s="1"/>
-      <c r="J62" s="1"/>
-      <c r="K62" s="1"/>
-      <c r="L62" s="1"/>
+      <c r="J62" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="L62" s="1" t="s">
+        <v>351</v>
+      </c>
       <c r="M62" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N62" s="1"/>
-      <c r="O62" s="1"/>
-      <c r="P62" s="1"/>
-      <c r="Q62" s="1"/>
+        <v>347</v>
+      </c>
+      <c r="N62" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O62" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="P62" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="Q62" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="R62" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S62" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T62" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U62" s="1"/>
       <c r="V62" s="1" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="63" spans="1:22">
       <c r="A63" s="1" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="B63" s="1">
         <v>31489362</v>
@@ -9275,48 +9289,34 @@
         <v>347</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G63" s="1"/>
       <c r="H63" s="1" t="s">
         <v>348</v>
       </c>
       <c r="I63" s="1"/>
-      <c r="J63" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="K63" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="L63" s="1" t="s">
-        <v>353</v>
-      </c>
+      <c r="J63" s="1"/>
+      <c r="K63" s="1"/>
+      <c r="L63" s="1"/>
       <c r="M63" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="N63" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O63" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="P63" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="Q63" s="1" t="s">
-        <v>53</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N63" s="1"/>
+      <c r="O63" s="1"/>
+      <c r="P63" s="1"/>
+      <c r="Q63" s="1"/>
       <c r="R63" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S63" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T63" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U63" s="1"/>
       <c r="V63" s="1" t="s">
@@ -9366,7 +9366,7 @@
         <v>362</v>
       </c>
       <c r="P64" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q64" s="1" t="s">
         <v>33</v>
@@ -9447,49 +9447,39 @@
         <v>368</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
-      <c r="J66" s="1" t="s">
-        <v>367</v>
-      </c>
+      <c r="J66" s="1"/>
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
-      <c r="M66" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="N66" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O66" s="1" t="s">
-        <v>369</v>
-      </c>
+      <c r="M66" s="1"/>
+      <c r="N66" s="1"/>
+      <c r="O66" s="1"/>
       <c r="P66" s="1"/>
-      <c r="Q66" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="Q66" s="1"/>
       <c r="R66" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S66" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T66" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U66" s="1"/>
       <c r="V66" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="67" spans="1:22">
       <c r="A67" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B67" s="1">
         <v>31544182</v>
@@ -9501,30 +9491,40 @@
         <v>368</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
-      <c r="J67" s="1"/>
+      <c r="J67" s="1" t="s">
+        <v>367</v>
+      </c>
       <c r="K67" s="1"/>
       <c r="L67" s="1"/>
-      <c r="M67" s="1"/>
-      <c r="N67" s="1"/>
-      <c r="O67" s="1"/>
+      <c r="M67" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="N67" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O67" s="1" t="s">
+        <v>371</v>
+      </c>
       <c r="P67" s="1"/>
-      <c r="Q67" s="1"/>
+      <c r="Q67" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="R67" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S67" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U67" s="1"/>
       <c r="V67" s="1" t="s">
@@ -9601,7 +9601,7 @@
         <v>379</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L69" s="1" t="s">
         <v>380</v>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="P69" s="1"/>
       <c r="Q69" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R69" s="1" t="s">
         <v>34</v>
@@ -9719,7 +9719,7 @@
       </c>
       <c r="P71" s="1"/>
       <c r="Q71" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R71" s="1" t="s">
         <v>34</v>
@@ -9759,7 +9759,7 @@
         <v>394</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L72" s="1" t="s">
         <v>395</v>
@@ -9817,7 +9817,7 @@
         <v>401</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L73" s="1" t="s">
         <v>402</v>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="P74" s="1"/>
       <c r="Q74" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R74" s="1" t="s">
         <v>34</v>
@@ -10149,7 +10149,7 @@
         <v>441</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L79" s="1" t="s">
         <v>189</v>
@@ -10207,7 +10207,7 @@
         <v>447</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L80" s="1" t="s">
         <v>189</v>
@@ -10253,13 +10253,13 @@
         <v>27</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H81" s="1" t="s">
         <v>450</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J81" s="1"/>
       <c r="K81" s="1"/>
@@ -10307,10 +10307,10 @@
         <v>454</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M82" s="1"/>
       <c r="N82" s="1" t="s">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="P83" s="1"/>
       <c r="Q83" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R83" s="1" t="s">
         <v>34</v>
@@ -10433,7 +10433,7 @@
         <v>470</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L84" s="1" t="s">
         <v>471</v>
@@ -10532,7 +10532,7 @@
         <v>34</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G86" s="1"/>
       <c r="H86" s="1"/>
@@ -10550,14 +10550,14 @@
         <v>484</v>
       </c>
       <c r="N86" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="O86" s="1" t="s">
         <v>485</v>
       </c>
       <c r="P86" s="1"/>
       <c r="Q86" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R86" s="1" t="s">
         <v>34</v>
@@ -10713,10 +10713,10 @@
         <v>503</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M89" s="1" t="s">
         <v>502</v>
@@ -10815,10 +10815,10 @@
         <v>511</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M91" s="1" t="s">
         <v>510</v>
@@ -10923,7 +10923,7 @@
         <v>522</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L93" s="1" t="s">
         <v>523</v>
@@ -11103,7 +11103,7 @@
         <v>545</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L96" s="1"/>
       <c r="M96" s="1" t="s">
@@ -11160,7 +11160,7 @@
         <v>551</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M97" s="1"/>
       <c r="N97" s="1" t="s">
@@ -11215,7 +11215,7 @@
         <v>558</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L98" s="1"/>
       <c r="M98" s="1" t="s">
@@ -11269,7 +11269,7 @@
         <v>564</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J99" s="1" t="s">
         <v>565</v>
@@ -11291,7 +11291,7 @@
       </c>
       <c r="P99" s="1"/>
       <c r="Q99" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R99" s="1" t="s">
         <v>34</v>
@@ -11333,10 +11333,10 @@
         <v>572</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M100" s="1" t="s">
         <v>570</v>
@@ -11349,7 +11349,7 @@
       </c>
       <c r="P100" s="1"/>
       <c r="Q100" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R100" s="1" t="s">
         <v>34</v>
@@ -11461,7 +11461,7 @@
       </c>
       <c r="P102" s="1"/>
       <c r="Q102" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R102" s="1" t="s">
         <v>34</v>
@@ -11551,10 +11551,10 @@
         <v>594</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M104" s="1" t="s">
         <v>592</v>
@@ -11567,7 +11567,7 @@
       </c>
       <c r="P104" s="1"/>
       <c r="Q104" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R104" s="1" t="s">
         <v>34</v>
@@ -11667,7 +11667,7 @@
         <v>606</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="L106" s="1" t="s">
         <v>31</v>
@@ -11775,7 +11775,7 @@
         <v>616</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L108" s="1" t="s">
         <v>617</v>
@@ -11885,13 +11885,13 @@
         <v>27</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J110" s="1" t="s">
         <v>629</v>
@@ -11999,10 +11999,10 @@
         <v>641</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M112" s="1"/>
       <c r="N112" s="1" t="s">
@@ -12057,10 +12057,10 @@
         <v>647</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M113" s="1" t="s">
         <v>645</v>
@@ -12167,7 +12167,7 @@
         <v>657</v>
       </c>
       <c r="K115" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L115" s="1" t="s">
         <v>658</v>
@@ -12181,7 +12181,7 @@
       </c>
       <c r="P115" s="1"/>
       <c r="Q115" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R115" s="1" t="s">
         <v>34</v>
@@ -12219,10 +12219,10 @@
         <v>662</v>
       </c>
       <c r="K116" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L116" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M116" s="1" t="s">
         <v>663</v>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="P117" s="1"/>
       <c r="Q117" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R117" s="1" t="s">
         <v>34</v>
@@ -12424,7 +12424,7 @@
         <v>34</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G120" s="1" t="s">
         <v>28</v>
@@ -12448,7 +12448,7 @@
         <v>682</v>
       </c>
       <c r="N120" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="O120" s="1" t="s">
         <v>686</v>
@@ -12501,7 +12501,7 @@
         <v>691</v>
       </c>
       <c r="K121" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L121" s="1" t="s">
         <v>380</v>
@@ -12559,10 +12559,10 @@
         <v>696</v>
       </c>
       <c r="K122" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L122" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M122" s="1" t="s">
         <v>697</v>
@@ -12575,7 +12575,7 @@
       </c>
       <c r="P122" s="1"/>
       <c r="Q122" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R122" s="1" t="s">
         <v>34</v>
@@ -12604,7 +12604,7 @@
         <v>34</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G123" s="1" t="s">
         <v>28</v>
@@ -12709,10 +12709,10 @@
         <v>707</v>
       </c>
       <c r="K125" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M125" s="1"/>
       <c r="N125" s="1" t="s">
@@ -12752,7 +12752,7 @@
         <v>34</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G126" s="1"/>
       <c r="H126" s="1"/>
@@ -12792,7 +12792,7 @@
         <v>34</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G127" s="1"/>
       <c r="H127" s="1"/>
@@ -12898,7 +12898,7 @@
         <v>59</v>
       </c>
       <c r="L129" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M129" s="1" t="s">
         <v>723</v>
@@ -12911,7 +12911,7 @@
       </c>
       <c r="P129" s="1"/>
       <c r="Q129" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R129" s="1" t="s">
         <v>34</v>
@@ -12954,7 +12954,7 @@
         <v>730</v>
       </c>
       <c r="L130" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M130" s="1" t="s">
         <v>727</v>
@@ -13067,7 +13067,7 @@
       </c>
       <c r="P132" s="1"/>
       <c r="Q132" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R132" s="1" t="s">
         <v>34</v>
@@ -13172,7 +13172,7 @@
         <v>756</v>
       </c>
       <c r="L134" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M134" s="1" t="s">
         <v>752</v>
@@ -13337,7 +13337,7 @@
         <v>775</v>
       </c>
       <c r="K137" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L137" s="1" t="s">
         <v>776</v>
@@ -13353,7 +13353,7 @@
       </c>
       <c r="P137" s="1"/>
       <c r="Q137" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R137" s="1" t="s">
         <v>34</v>
@@ -13395,10 +13395,10 @@
         <v>782</v>
       </c>
       <c r="K138" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M138" s="1" t="s">
         <v>780</v>
@@ -13511,7 +13511,7 @@
         <v>794</v>
       </c>
       <c r="K140" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="L140" s="1" t="s">
         <v>795</v>
@@ -13525,7 +13525,7 @@
       </c>
       <c r="P140" s="1"/>
       <c r="Q140" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R140" s="1" t="s">
         <v>34</v>
@@ -13565,7 +13565,7 @@
         <v>800</v>
       </c>
       <c r="K141" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L141" s="1" t="s">
         <v>801</v>
@@ -13643,7 +13643,7 @@
       </c>
       <c r="P142" s="1"/>
       <c r="Q142" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R142" s="1" t="s">
         <v>26</v>
@@ -13686,7 +13686,7 @@
         <v>59</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M143" s="1" t="s">
         <v>815</v>
@@ -13743,10 +13743,10 @@
         <v>820</v>
       </c>
       <c r="K144" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L144" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M144" s="1" t="s">
         <v>821</v>
@@ -13850,7 +13850,7 @@
         <v>34</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G146" s="1"/>
       <c r="H146" s="1"/>
@@ -13868,14 +13868,14 @@
         <v>834</v>
       </c>
       <c r="N146" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="O146" s="1" t="s">
         <v>835</v>
       </c>
       <c r="P146" s="1"/>
       <c r="Q146" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R146" s="1" t="s">
         <v>34</v>
@@ -14013,10 +14013,10 @@
         <v>849</v>
       </c>
       <c r="K149" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L149" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M149" s="1" t="s">
         <v>848</v>
@@ -14075,7 +14075,7 @@
         <v>855</v>
       </c>
       <c r="K150" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L150" s="1"/>
       <c r="M150" s="1" t="s">
@@ -14089,7 +14089,7 @@
       </c>
       <c r="P150" s="1"/>
       <c r="Q150" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R150" s="1" t="s">
         <v>26</v>
@@ -14125,13 +14125,13 @@
         <v>27</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H151" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I151" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J151" s="1" t="s">
         <v>861</v>
@@ -14140,7 +14140,7 @@
         <v>59</v>
       </c>
       <c r="L151" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M151" s="1" t="s">
         <v>860</v>
@@ -14153,7 +14153,7 @@
       </c>
       <c r="P151" s="1"/>
       <c r="Q151" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R151" s="1" t="s">
         <v>34</v>
@@ -14193,7 +14193,7 @@
         <v>866</v>
       </c>
       <c r="K152" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L152" s="1" t="s">
         <v>31</v>
@@ -14308,7 +14308,7 @@
         <v>59</v>
       </c>
       <c r="L154" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M154" s="1" t="s">
         <v>877</v>
@@ -14438,7 +14438,7 @@
         <v>34</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G157" s="1"/>
       <c r="H157" s="1"/>
@@ -14447,14 +14447,14 @@
         <v>890</v>
       </c>
       <c r="K157" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="L157" s="1" t="s">
         <v>189</v>
       </c>
       <c r="M157" s="1"/>
       <c r="N157" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="O157" s="1" t="s">
         <v>891</v>
@@ -14643,14 +14643,14 @@
         <v>27</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="H161" s="1" t="s">
         <v>905</v>
       </c>
       <c r="I161" s="1"/>
       <c r="J161" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K161" s="1" t="s">
         <v>59</v>
@@ -14807,7 +14807,7 @@
         <v>921</v>
       </c>
       <c r="K164" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L164" s="1" t="s">
         <v>630</v>
@@ -14869,7 +14869,7 @@
         <v>928</v>
       </c>
       <c r="K165" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L165" s="1" t="s">
         <v>929</v>
@@ -14943,7 +14943,7 @@
         <v>938</v>
       </c>
       <c r="Q166" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R166" s="1" t="s">
         <v>26</v>
@@ -15046,7 +15046,7 @@
         <v>477</v>
       </c>
       <c r="L168" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="M168" s="1"/>
       <c r="N168" s="1" t="s">
@@ -15057,7 +15057,7 @@
       </c>
       <c r="P168" s="1"/>
       <c r="Q168" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R168" s="1" t="s">
         <v>34</v>
@@ -15103,7 +15103,7 @@
         <v>955</v>
       </c>
       <c r="K169" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L169" s="1" t="s">
         <v>189</v>
@@ -15162,7 +15162,7 @@
         <v>961</v>
       </c>
       <c r="L170" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M170" s="1"/>
       <c r="N170" s="1" t="s">
@@ -15207,7 +15207,7 @@
         <v>27</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H171" s="1" t="s">
         <v>966</v>
@@ -15277,7 +15277,7 @@
         <v>974</v>
       </c>
       <c r="K172" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="L172" s="1" t="s">
         <v>975</v>
@@ -15322,7 +15322,7 @@
         <v>34</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G173" s="1" t="s">
         <v>28</v>
@@ -15346,7 +15346,7 @@
         <v>982</v>
       </c>
       <c r="N173" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="O173" s="1" t="s">
         <v>983</v>
@@ -15399,10 +15399,10 @@
         <v>990</v>
       </c>
       <c r="K174" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="L174" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M174" s="1" t="s">
         <v>991</v>
@@ -15415,7 +15415,7 @@
       </c>
       <c r="P174" s="1"/>
       <c r="Q174" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R174" s="1" t="s">
         <v>34</v>
@@ -15515,7 +15515,7 @@
       </c>
       <c r="P176" s="1"/>
       <c r="Q176" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R176" s="1" t="s">
         <v>26</v>
@@ -15579,7 +15579,7 @@
       </c>
       <c r="P177" s="1"/>
       <c r="Q177" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R177" s="1" t="s">
         <v>34</v>
@@ -15688,7 +15688,7 @@
         <v>1024</v>
       </c>
       <c r="L179" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M179" s="1" t="s">
         <v>1025</v>
@@ -15735,7 +15735,7 @@
         <v>27</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H180" s="1"/>
       <c r="I180" s="1"/>
@@ -15843,7 +15843,7 @@
       </c>
       <c r="P182" s="1"/>
       <c r="Q182" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R182" s="1" t="s">
         <v>34</v>
@@ -16073,7 +16073,7 @@
       </c>
       <c r="P186" s="1"/>
       <c r="Q186" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R186" s="1" t="s">
         <v>34</v>
@@ -16174,7 +16174,7 @@
         <v>1075</v>
       </c>
       <c r="L188" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M188" s="1" t="s">
         <v>1076</v>
@@ -16234,7 +16234,7 @@
         <v>1083</v>
       </c>
       <c r="L189" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="M189" s="1" t="s">
         <v>1080</v>
@@ -16295,10 +16295,10 @@
         <v>1089</v>
       </c>
       <c r="K190" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L190" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="M190" s="1" t="s">
         <v>1087</v>
@@ -16461,7 +16461,7 @@
         <v>1107</v>
       </c>
       <c r="K193" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L193" s="1" t="s">
         <v>1108</v>
@@ -16475,7 +16475,7 @@
       </c>
       <c r="P193" s="1"/>
       <c r="Q193" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R193" s="1" t="s">
         <v>34</v>
@@ -16565,13 +16565,13 @@
         <v>27</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H195" s="1" t="s">
         <v>1121</v>
       </c>
       <c r="I195" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J195" s="1" t="s">
         <v>1122</v>
@@ -16580,7 +16580,7 @@
         <v>1123</v>
       </c>
       <c r="L195" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M195" s="1" t="s">
         <v>1120</v>
@@ -16649,7 +16649,7 @@
       </c>
       <c r="P196" s="1"/>
       <c r="Q196" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R196" s="1" t="s">
         <v>34</v>
@@ -16698,7 +16698,7 @@
         <v>59</v>
       </c>
       <c r="L197" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M197" s="1"/>
       <c r="N197" s="1" t="s">
@@ -16909,13 +16909,13 @@
         <v>27</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H201" s="1" t="s">
         <v>1158</v>
       </c>
       <c r="I201" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J201" s="1"/>
       <c r="K201" s="1"/>
@@ -17089,7 +17089,7 @@
       </c>
       <c r="P204" s="1"/>
       <c r="Q204" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R204" s="1" t="s">
         <v>34</v>
@@ -17145,7 +17145,7 @@
       </c>
       <c r="P205" s="1"/>
       <c r="Q205" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R205" s="1" t="s">
         <v>26</v>
@@ -17189,10 +17189,10 @@
         <v>1190</v>
       </c>
       <c r="K206" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L206" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M206" s="1" t="s">
         <v>1188</v>
@@ -17205,7 +17205,7 @@
       </c>
       <c r="P206" s="1"/>
       <c r="Q206" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R206" s="1" t="s">
         <v>26</v>
@@ -17265,7 +17265,7 @@
       </c>
       <c r="P207" s="1"/>
       <c r="Q207" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R207" s="1" t="s">
         <v>34</v>
@@ -17327,7 +17327,7 @@
       </c>
       <c r="P208" s="1"/>
       <c r="Q208" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R208" s="1" t="s">
         <v>34</v>
@@ -17427,13 +17427,13 @@
         <v>185</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H210" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I210" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J210" s="1" t="s">
         <v>1216</v>
@@ -17563,10 +17563,10 @@
         <v>1234</v>
       </c>
       <c r="K212" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L212" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M212" s="1" t="s">
         <v>1235</v>
@@ -17637,7 +17637,7 @@
       </c>
       <c r="P213" s="1"/>
       <c r="Q213" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R213" s="1" t="s">
         <v>34</v>
@@ -17699,7 +17699,7 @@
       </c>
       <c r="P214" s="1"/>
       <c r="Q214" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R214" s="1" t="s">
         <v>34</v>
@@ -17785,7 +17785,7 @@
         <v>926</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H216" s="1"/>
       <c r="I216" s="1"/>
@@ -17851,7 +17851,7 @@
         <v>1259</v>
       </c>
       <c r="K217" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="L217" s="1" t="s">
         <v>189</v>
@@ -17980,7 +17980,7 @@
         <v>1272</v>
       </c>
       <c r="L219" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M219" s="1" t="s">
         <v>1273</v>
@@ -18040,7 +18040,7 @@
         <v>1280</v>
       </c>
       <c r="L220" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M220" s="1" t="s">
         <v>1281</v>
@@ -18111,7 +18111,7 @@
       </c>
       <c r="P221" s="1"/>
       <c r="Q221" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R221" s="1" t="s">
         <v>26</v>
@@ -18158,7 +18158,7 @@
         <v>1294</v>
       </c>
       <c r="L222" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="M222" s="1" t="s">
         <v>1293</v>
@@ -18519,13 +18519,13 @@
         <v>27</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H228" s="1" t="s">
         <v>1335</v>
       </c>
       <c r="I228" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J228" s="1" t="s">
         <v>1336</v>
@@ -18547,7 +18547,7 @@
       </c>
       <c r="P228" s="1"/>
       <c r="Q228" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R228" s="1" t="s">
         <v>34</v>
@@ -18595,10 +18595,10 @@
         <v>1345</v>
       </c>
       <c r="K229" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="L229" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M229" s="1" t="s">
         <v>1346</v>
@@ -18803,7 +18803,7 @@
       </c>
       <c r="P232" s="1"/>
       <c r="Q232" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R232" s="1" t="s">
         <v>34</v>
@@ -18851,7 +18851,7 @@
         <v>1379</v>
       </c>
       <c r="K233" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L233" s="1" t="s">
         <v>1380</v>
@@ -19055,7 +19055,7 @@
       </c>
       <c r="P236" s="1"/>
       <c r="Q236" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R236" s="1" t="s">
         <v>34</v>
@@ -19418,7 +19418,7 @@
         <v>1437</v>
       </c>
       <c r="L242" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M242" s="1" t="s">
         <v>1442</v>
@@ -19535,10 +19535,10 @@
         <v>1454</v>
       </c>
       <c r="K244" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="L244" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="M244" s="1" t="s">
         <v>1453</v>
@@ -19551,7 +19551,7 @@
       </c>
       <c r="P244" s="1"/>
       <c r="Q244" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R244" s="1" t="s">
         <v>34</v>
@@ -19595,10 +19595,10 @@
         <v>1460</v>
       </c>
       <c r="K245" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L245" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M245" s="1" t="s">
         <v>1459</v>
@@ -19647,22 +19647,22 @@
         <v>27</v>
       </c>
       <c r="G246" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H246" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I246" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J246" s="1" t="s">
         <v>1460</v>
       </c>
       <c r="K246" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L246" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M246" s="1" t="s">
         <v>1464</v>
@@ -19850,7 +19850,7 @@
         <v>280</v>
       </c>
       <c r="L249" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M249" s="1" t="s">
         <v>1487</v>
@@ -19863,7 +19863,7 @@
       </c>
       <c r="P249" s="1"/>
       <c r="Q249" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R249" s="1" t="s">
         <v>34</v>
@@ -19912,7 +19912,7 @@
         <v>280</v>
       </c>
       <c r="L250" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M250" s="1" t="s">
         <v>1487</v>
@@ -19925,7 +19925,7 @@
       </c>
       <c r="P250" s="1"/>
       <c r="Q250" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R250" s="1" t="s">
         <v>34</v>
@@ -20045,7 +20045,7 @@
       </c>
       <c r="P252" s="1"/>
       <c r="Q252" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R252" s="1" t="s">
         <v>34</v>
@@ -20456,7 +20456,7 @@
         <v>1555</v>
       </c>
       <c r="L259" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M259" s="1" t="s">
         <v>1551</v>
@@ -20469,7 +20469,7 @@
       </c>
       <c r="P259" s="1"/>
       <c r="Q259" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R259" s="1" t="s">
         <v>34</v>
@@ -20518,7 +20518,7 @@
         <v>1555</v>
       </c>
       <c r="L260" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M260" s="1" t="s">
         <v>1561</v>
@@ -20531,7 +20531,7 @@
       </c>
       <c r="P260" s="1"/>
       <c r="Q260" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R260" s="1" t="s">
         <v>34</v>
@@ -20578,7 +20578,7 @@
         <v>477</v>
       </c>
       <c r="L261" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M261" s="1" t="s">
         <v>1569</v>
@@ -20591,7 +20591,7 @@
       </c>
       <c r="P261" s="1"/>
       <c r="Q261" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R261" s="1" t="s">
         <v>34</v>
@@ -20691,13 +20691,13 @@
         <v>27</v>
       </c>
       <c r="G263" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H263" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I263" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J263" s="1" t="s">
         <v>1582</v>
@@ -20839,7 +20839,7 @@
       </c>
       <c r="P265" s="1"/>
       <c r="Q265" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R265" s="1" t="s">
         <v>34</v>
@@ -20903,7 +20903,7 @@
       </c>
       <c r="P266" s="1"/>
       <c r="Q266" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R266" s="1" t="s">
         <v>34</v>
@@ -20952,7 +20952,7 @@
         <v>730</v>
       </c>
       <c r="L267" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M267" s="1" t="s">
         <v>1613</v>
@@ -21014,7 +21014,7 @@
         <v>730</v>
       </c>
       <c r="L268" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M268" s="1" t="s">
         <v>1613</v>
@@ -21078,7 +21078,7 @@
         <v>59</v>
       </c>
       <c r="L269" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M269" s="1" t="s">
         <v>1625</v>
@@ -21142,7 +21142,7 @@
         <v>59</v>
       </c>
       <c r="L270" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M270" s="1" t="s">
         <v>1632</v>
@@ -21193,13 +21193,13 @@
         <v>195</v>
       </c>
       <c r="G271" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H271" s="1" t="s">
         <v>1641</v>
       </c>
       <c r="I271" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J271" s="1" t="s">
         <v>1642</v>
@@ -21223,7 +21223,7 @@
         <v>1646</v>
       </c>
       <c r="Q271" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R271" s="1" t="s">
         <v>34</v>
@@ -21261,13 +21261,13 @@
         <v>195</v>
       </c>
       <c r="G272" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H272" s="1" t="s">
         <v>1641</v>
       </c>
       <c r="I272" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J272" s="1" t="s">
         <v>1642</v>
@@ -21291,7 +21291,7 @@
         <v>1646</v>
       </c>
       <c r="Q272" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R272" s="1" t="s">
         <v>34</v>
@@ -21402,7 +21402,7 @@
         <v>1353</v>
       </c>
       <c r="L274" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="M274" s="1" t="s">
         <v>1664</v>
@@ -21415,7 +21415,7 @@
       </c>
       <c r="P274" s="1"/>
       <c r="Q274" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R274" s="1" t="s">
         <v>34</v>
@@ -21479,7 +21479,7 @@
       </c>
       <c r="P275" s="1"/>
       <c r="Q275" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R275" s="1" t="s">
         <v>34</v>
@@ -21539,7 +21539,7 @@
       </c>
       <c r="P276" s="1"/>
       <c r="Q276" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R276" s="1" t="s">
         <v>34</v>
@@ -22072,7 +22072,7 @@
         <v>1746</v>
       </c>
       <c r="L285" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M285" s="1" t="s">
         <v>1743</v>
@@ -22085,7 +22085,7 @@
       </c>
       <c r="P285" s="1"/>
       <c r="Q285" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R285" s="1" t="s">
         <v>34</v>
@@ -22130,7 +22130,7 @@
         <v>1751</v>
       </c>
       <c r="L286" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M286" s="1" t="s">
         <v>1743</v>
@@ -22143,7 +22143,7 @@
       </c>
       <c r="P286" s="1"/>
       <c r="Q286" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R286" s="1" t="s">
         <v>34</v>
